--- a/out/MLP-Mamba1_repeat_2_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.358776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001446788583160378</v>
+        <v>-0.0001375234126630239</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1662082200690484</v>
+        <v>-0.1579879873436859</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.358776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8815939771807735</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8815939771807735</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.166477454133328</v>
+        <v>-0.1582446333882272</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.447872154367124</v>
+        <v>0.4283378551738887</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7301267855378213</v>
+        <v>0.6992535013266793</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03191076037898097</v>
+        <v>0.03051894566280475</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.958776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3453577891686992</v>
+        <v>0.3312665098784594</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05596072935461647</v>
+        <v>0.05351983224341474</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.958776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4253577649402572</v>
+        <v>0.4077772275640904</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06798567725616877</v>
+        <v>0.06502058732025365</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5053630654048971</v>
+        <v>0.4842932208569604</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01799071359654017</v>
+        <v>0.01720591149552624</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4732720156328087</v>
+        <v>0.4536017728347986</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009994478788653016</v>
+        <v>0.009558634174589331</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4752535960249403</v>
+        <v>0.4554967295306599</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02099948461109135</v>
+        <v>0.02008418567808663</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.958776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5072720424121632</v>
+        <v>0.4861184717419974</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008247255676078983</v>
+        <v>0.007887566809657577</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5027483519644507</v>
+        <v>0.4817920525699325</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005871854005535577</v>
+        <v>0.00561483867039475</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5062418803276962</v>
+        <v>0.4851326005783878</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002308846602832894</v>
+        <v>0.002207004762919474</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5049814194167482</v>
+        <v>0.4839270301451515</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001308284018292068</v>
+        <v>0.001251251731112717</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5052877925539792</v>
+        <v>0.4842198812095213</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004952812922704135</v>
+        <v>0.0004729682768874608</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5049690212553875</v>
+        <v>0.4839147369205495</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002295045744476447</v>
+        <v>0.0002195959304568991</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5049323932520531</v>
+        <v>0.4838794453117223</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.057648120152129e-05</v>
+        <v>7.734718002410539e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5048646528202573</v>
+        <v>0.4838143553374407</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.028024483792712e-05</v>
+        <v>1.932627333460911e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5048242245566037</v>
+        <v>0.4837755822452032</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>6.924643791475056e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5048192044512685</v>
+        <v>0.483770563629152</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5048151864069249</v>
+        <v>0.4837665088363164</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.504812751736734</v>
+        <v>0.4837638914328977</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5048072344947443</v>
+        <v>0.4837583741909079</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5048009105007364</v>
+        <v>0.4837520501969</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5047955427121581</v>
+        <v>0.4837466824083216</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5047955794606498</v>
+        <v>0.4837467191568133</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5047956897061253</v>
+        <v>0.4837468294022889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5047957632031089</v>
+        <v>0.4837469028992725</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5047959469455681</v>
+        <v>0.4837470866417317</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5047974903822245</v>
+        <v>0.4837486300783881</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5047989603218976</v>
+        <v>0.4837501000180612</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5048002097706197</v>
+        <v>0.4837513494667832</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5048015694648169</v>
+        <v>0.4837527091609805</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5047993645553077</v>
+        <v>0.4837505042514713</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5047989603218976</v>
+        <v>0.4837501000180612</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.358776160273009</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5047981151065857</v>
+        <v>0.4837492548027493</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.504798666333963</v>
+        <v>0.4837498060301265</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5047983355975365</v>
+        <v>0.4837494752937001</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.358776160273009</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5047980416096021</v>
+        <v>0.4837491813057657</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5047981151065857</v>
+        <v>0.4837492548027493</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5047976741246837</v>
+        <v>0.4837488138208473</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5047975638792082</v>
+        <v>0.4837487035753718</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5047975271307165</v>
+        <v>0.4837486668268801</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5047976741246837</v>
+        <v>0.4837488138208473</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5047971963942901</v>
+        <v>0.4837483360904536</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5047981518550774</v>
+        <v>0.483749291551241</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5047981151065857</v>
+        <v>0.4837492548027493</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5047977843701593</v>
+        <v>0.4837489240663229</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5047982253520612</v>
+        <v>0.4837493650482248</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5047976006277001</v>
+        <v>0.4837487403238637</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5047974168852409</v>
+        <v>0.4837485565814045</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5047970126518309</v>
+        <v>0.4837481523479945</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5047961674365189</v>
+        <v>0.4837473071326825</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.358776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5047961306880272</v>
+        <v>0.4837472703841909</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5047962776819945</v>
+        <v>0.4837474173781581</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8815939771807735</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5047962041850108</v>
+        <v>0.4837473438811745</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5047962776819945</v>
+        <v>0.4837474173781581</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5047963144304864</v>
+        <v>0.48374745412665</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5047962041850108</v>
+        <v>0.4837473438811745</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5047966451669128</v>
+        <v>0.4837477848630764</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8815939771807735</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5047965349214373</v>
+        <v>0.4837476746176009</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5047964981729454</v>
+        <v>0.483747637869109</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5047964246759618</v>
+        <v>0.4837475643721253</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5047963879274701</v>
+        <v>0.4837475276236336</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5047961674365189</v>
+        <v>0.4837473071326825</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5047960939395353</v>
+        <v>0.4837472336356989</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5047960204425517</v>
+        <v>0.4837471601387153</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5047960571910436</v>
+        <v>0.4837471968872072</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5047959469455681</v>
+        <v>0.4837470866417317</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5047960571910436</v>
+        <v>0.4837471968872072</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.958776160273009</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5047963511789781</v>
+        <v>0.4837474908751417</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_2_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001446788583160378</v>
+        <v>-0.0001147858504502801</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1662082200690484</v>
+        <v>-0.1318668955126306</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1663528989273644</v>
+        <v>-0.1319816813630809</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.166477454133328</v>
+        <v>-0.1320826763740562</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.447872154367124</v>
+        <v>0.3631550588017399</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7301267855378213</v>
+        <v>0.5949247122406061</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03191076037898097</v>
+        <v>0.02587468510680326</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3453577891686992</v>
+        <v>0.2829365564124733</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05596072935461647</v>
+        <v>0.04537538162581548</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4253577649402572</v>
+        <v>0.3478041833164999</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06798567725616877</v>
+        <v>0.05512572988532174</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5053630654048971</v>
+        <v>0.4126763114546158</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01799071359654017</v>
+        <v>0.01458781432675267</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4732720156328087</v>
+        <v>0.3866552048924039</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009994478788653016</v>
+        <v>0.008103250686381725</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4752535960249403</v>
+        <v>0.3882610282365515</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02099948461109135</v>
+        <v>0.0170270256055591</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5072720424121632</v>
+        <v>0.4142227881560109</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008247255676078983</v>
+        <v>0.006686181774337597</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5027483519644507</v>
+        <v>0.4105538329105067</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005871854005535577</v>
+        <v>0.004760995778483944</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5062418803276962</v>
+        <v>0.4133856431137607</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002308846602832894</v>
+        <v>0.001870247745605766</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5049814194167482</v>
+        <v>0.4123627923436202</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001308284018292068</v>
+        <v>0.001060116498403543</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5052877925539792</v>
+        <v>0.4126103261908344</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004952812922704135</v>
+        <v>0.000400157384585194</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5049690212553875</v>
+        <v>0.4123508481471974</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002295045744476447</v>
+        <v>0.0001854661567109978</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5049323932520531</v>
+        <v>0.4123201596750056</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.057648120152129e-05</v>
+        <v>6.44299753144418e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5048646528202573</v>
+        <v>0.412264201591108</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.028024483792712e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5048242245566037</v>
+        <v>0.4122303955024029</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5048192044512685</v>
+        <v>0.412225379120278</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5048151864069249</v>
+        <v>0.4122211789109556</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.504812751736734</v>
+        <v>0.4122181950318499</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5048072344947443</v>
+        <v>0.4122127512868435</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5048009105007364</v>
+        <v>0.4122067585534132</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5047955427121581</v>
+        <v>0.4122013907648348</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5047955794606498</v>
+        <v>0.4122014275133265</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5047956897061253</v>
+        <v>0.4122015377588021</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5047957632031089</v>
+        <v>0.4122016112557857</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5047959469455681</v>
+        <v>0.4122017949982448</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5047974903822245</v>
+        <v>0.4122033384349013</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5047989603218976</v>
+        <v>0.4122048083745744</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5048002097706197</v>
+        <v>0.4122060578232964</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5048015694648169</v>
+        <v>0.4122074175174937</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5047993645553077</v>
+        <v>0.4122052126079844</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5047989603218976</v>
+        <v>0.4122048083745744</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5047981151065857</v>
+        <v>0.4122039631592624</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.504798666333963</v>
+        <v>0.4122045143866397</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5047983355975365</v>
+        <v>0.4122041836502133</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5047980416096021</v>
+        <v>0.4122038896622788</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5047981151065857</v>
+        <v>0.4122039631592624</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5047976741246837</v>
+        <v>0.4122035221773605</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5047975638792082</v>
+        <v>0.4122034119318849</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5047975271307165</v>
+        <v>0.4122033751833932</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5047976741246837</v>
+        <v>0.4122035221773605</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5047971963942901</v>
+        <v>0.4122030444469669</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5047981518550774</v>
+        <v>0.4122039999077541</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5047981151065857</v>
+        <v>0.4122039631592624</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5047977843701593</v>
+        <v>0.412203632422836</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5047982253520612</v>
+        <v>0.412204073404738</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5047976006277001</v>
+        <v>0.4122034486803769</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5047974168852409</v>
+        <v>0.4122032649379177</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5047970126518309</v>
+        <v>0.4122028607045077</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5047961674365189</v>
+        <v>0.4122020154891957</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5047961306880272</v>
+        <v>0.412201978740704</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5047962776819945</v>
+        <v>0.4122021257346712</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5047962041850108</v>
+        <v>0.4122020522376876</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5047962776819945</v>
+        <v>0.4122021257346712</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5047963144304864</v>
+        <v>0.4122021624831632</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5047962041850108</v>
+        <v>0.4122020522376876</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5047966451669128</v>
+        <v>0.4122024932195896</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5047965349214373</v>
+        <v>0.412202382974114</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5047964981729454</v>
+        <v>0.4122023462256221</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5047964246759618</v>
+        <v>0.4122022727286385</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5047963879274701</v>
+        <v>0.4122022359801468</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5047961674365189</v>
+        <v>0.4122020154891957</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5047960939395353</v>
+        <v>0.4122019419922121</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5047960204425517</v>
+        <v>0.4122018684952284</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5047960571910436</v>
+        <v>0.4122019052437204</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5047959469455681</v>
+        <v>0.4122017949982448</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5047960571910436</v>
+        <v>0.4122019052437204</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5047963511789781</v>
+        <v>0.4122021992316549</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_2_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.506510853767395</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.097446509901492</v>
+        <v>0.2599999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5588412880897522</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.097446509901492</v>
+        <v>0.04999999999999971</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.6559196710586548</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4758383631706238</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.3920080363750458</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4621579051017761</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.5163360238075256</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4186424016952515</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4993880093097687</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4476161599159241</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.5695893168449402</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4753749072551727</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5312574505805969</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4867171943187714</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5455482602119446</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3759670853614807</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4456710815429688</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4553584456443787</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4853988289833069</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5125195384025574</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4480500519275665</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5451126098632812</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4889173805713654</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.593101978302002</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4381693601608276</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5306145548820496</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4766255617141724</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5504590272903442</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.5633201003074646</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5884035229682922</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.7123118042945862</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3510255813598633</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5832029581069946</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5670139789581299</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4123456478118896</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.6279172897338867</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4509689211845398</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4994779229164124</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.6245003342628479</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5534694194793701</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5856844186782837</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5903186202049255</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.7317274212837219</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.565312922000885</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001147858504502801</v>
+        <v>-0.0001132297395697096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1318668955126306</v>
+        <v>-0.1300792229893992</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.1222320273518562</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.6140308976173401</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.2339076548814774</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4217348992824554</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3318051397800446</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4698199033737183</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3710117936134338</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5520908832550049</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4111587107181549</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4599544107913971</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4215425848960876</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4224110543727875</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5149644613265991</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1319816813630809</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.6961955428123474</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1320826763740562</v>
+        <v>-0.1302860157581051</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3631550588017399</v>
+        <v>0.3364313446722635</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.2239489406347275</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5949247122406061</v>
+        <v>0.5432226340878866</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02587468510680326</v>
+        <v>0.0239706626721457</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5701884627342224</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2829365564124733</v>
+        <v>0.2541929419558563</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04537538162581548</v>
+        <v>0.04203624669638161</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.6582904458045959</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3478041833164999</v>
+        <v>0.3142870300491233</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05512572988532174</v>
+        <v>0.05106938708129904</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.2870840728282928</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4126763114546158</v>
+        <v>0.3743853010803733</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01458781432675267</v>
+        <v>0.01351423937528155</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3367099761962891</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3866552048924039</v>
+        <v>0.3502791906641927</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008103250686381725</v>
+        <v>0.007506349013754104</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.8285361528396606</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3882610282365515</v>
+        <v>0.351766467453772</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0170270256055591</v>
+        <v>0.01577426797503244</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.5341136455535889</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.297446509901492</v>
+        <v>0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4142227881560109</v>
+        <v>0.3758181862179595</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006686181774337597</v>
+        <v>0.006194485882865911</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.6855748295783997</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4105538329105067</v>
+        <v>0.3724187800890964</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004760995778483944</v>
+        <v>0.004409109010908583</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3191965818405151</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4133856431137607</v>
+        <v>0.3750416551579663</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001870247745605766</v>
+        <v>0.001733100734522361</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5964618921279907</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4123627923436202</v>
+        <v>0.3740935859290853</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001060116498403543</v>
+        <v>0.0009815044268860604</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.2856564819812775</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4126103261908344</v>
+        <v>0.3743224812434371</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000400157384585194</v>
+        <v>0.0003707981538181509</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3102104365825653</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4123508481471974</v>
+        <v>0.3740817844933211</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001854661567109978</v>
+        <v>0.0001711536709465875</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2305819988250732</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4123201596750056</v>
+        <v>0.3740530263687507</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.44299753144418e-05</v>
+        <v>5.958602354831795e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2319338619709015</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.412264201591108</v>
+        <v>0.3740008969771571</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.551038732133709e-05</v>
+        <v>1.407943006636009e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3933239281177521</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4122303955024029</v>
+        <v>0.373969408277363</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.49368653649805e-06</v>
+        <v>4.539715033180046e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3779951632022858</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.412225379120278</v>
+        <v>0.3739643933845221</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.523462176322937</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4122211789109556</v>
+        <v>0.3739601204669564</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3179396688938141</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4122181950318499</v>
+        <v>0.3739569528453916</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.213842362165451</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.650235870066816</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4122127512868435</v>
+        <v>0.3739515835184038</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2721230983734131</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4122067585534132</v>
+        <v>0.3739455907849735</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4024220705032349</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4122013907648348</v>
+        <v>0.3739402229963951</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3681215345859528</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4122014275133265</v>
+        <v>0.3739402597448868</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.450409471988678</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4122015377588021</v>
+        <v>0.3739403699903623</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4167593121528625</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4122016112557857</v>
+        <v>0.373940443487346</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.8047202825546265</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4122017949982448</v>
+        <v>0.3739406272298051</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.8230204582214355</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4122033384349013</v>
+        <v>0.3739421706664616</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.8548390865325928</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4122048083745744</v>
+        <v>0.3739436406061347</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.9087350964546204</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4122060578232964</v>
+        <v>0.3739448900548566</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9313003420829773</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4122074175174937</v>
+        <v>0.373946249749054</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.1127559244632721</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4122052126079844</v>
+        <v>0.3739440448395447</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3806303739547729</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4122048083745744</v>
+        <v>0.3739436406061347</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.7527236938476562</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4122039631592624</v>
+        <v>0.3739427953908227</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.386773556470871</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4122045143866397</v>
+        <v>0.3739433466181999</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3675996661186218</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4122041836502133</v>
+        <v>0.3739430158817735</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6358606219291687</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4122038896622788</v>
+        <v>0.3739427218938391</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.1950857192277908</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4122039631592624</v>
+        <v>0.3739427953908227</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.5294774174690247</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4122035221773605</v>
+        <v>0.3739423544089208</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4059231877326965</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4122034119318849</v>
+        <v>0.3739422441634452</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.5724329948425293</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4122033751833932</v>
+        <v>0.3739422074149535</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.1857801526784897</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4122035221773605</v>
+        <v>0.3739423544089208</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.9223608374595642</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4122030444469669</v>
+        <v>0.3739418766785271</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.7507257461547852</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4122039999077541</v>
+        <v>0.3739428321393144</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.277698278427124</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4122039631592624</v>
+        <v>0.3739427953908227</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5566800832748413</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.412203632422836</v>
+        <v>0.3739424646543963</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3355928063392639</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.412204073404738</v>
+        <v>0.3739429056362982</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2320923805236816</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4122034486803769</v>
+        <v>0.3739422809119371</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3058618009090424</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4122032649379177</v>
+        <v>0.373942097169478</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.1120200529694557</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4122028607045077</v>
+        <v>0.3739416929360679</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3010963499546051</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4122020154891957</v>
+        <v>0.373940847720756</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5510005950927734</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.412201978740704</v>
+        <v>0.3739408109722643</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3084949254989624</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4122021257346712</v>
+        <v>0.3739409579662315</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4190325736999512</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4122020522376876</v>
+        <v>0.3739408844692479</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.6626641154289246</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4122021257346712</v>
+        <v>0.3739409579662315</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2291880697011948</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4122021624831632</v>
+        <v>0.3739409947147234</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.7123171091079712</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4122020522376876</v>
+        <v>0.3739408844692479</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.2694237530231476</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4122024932195896</v>
+        <v>0.3739413254511498</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4564144909381866</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.412202382974114</v>
+        <v>0.3739412152056743</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3101788759231567</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4122023462256221</v>
+        <v>0.3739411784571824</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3081660866737366</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4122022727286385</v>
+        <v>0.3739411049601987</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2613233327865601</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4122022359801468</v>
+        <v>0.373941068211707</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2335698753595352</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4122020154891957</v>
+        <v>0.373940847720756</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3990555703639984</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4122019419922121</v>
+        <v>0.3739407742237724</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3496275842189789</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4122018684952284</v>
+        <v>0.3739407007267887</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.2564267516136169</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4122019052437204</v>
+        <v>0.3739407374752807</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4830233752727509</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4122017949982448</v>
+        <v>0.3739406272298051</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.6477704644203186</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.8600000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4122019052437204</v>
+        <v>0.3739407374752807</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.5355440378189087</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.297446509901492</v>
+        <v>1.280000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4122021992316549</v>
+        <v>0.3739410314632151</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_2_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000008.xlsx
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4456710815429688</v>
+        <v>0.445671021938324</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.5451126098632812</v>
+        <v>0.5451125502586365</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.5504590272903442</v>
+        <v>0.5504589676856995</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.5633201003074646</v>
+        <v>0.5633200407028198</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.5832029581069946</v>
+        <v>0.5832028985023499</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.5670139789581299</v>
+        <v>0.5670139193534851</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.4123456478118896</v>
+        <v>0.4123455882072449</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.6279172897338867</v>
+        <v>0.6279172301292419</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.5799999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.3318051397800446</v>
+        <v>0.3318051099777222</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.5520908832550049</v>
+        <v>0.5520908236503601</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.4215425848960876</v>
+        <v>0.42154261469841</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.8599999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.4224110543727875</v>
+        <v>0.4224111139774323</v>
       </c>
       <c r="JB57" t="n">
         <v>0.02000000000000007</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.2239489406347275</v>
+        <v>0.2239489704370499</v>
       </c>
       <c r="JB60" t="n">
         <v>0.5799999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.2870840728282928</v>
+        <v>0.2870841026306152</v>
       </c>
       <c r="JB63" t="n">
         <v>0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3367099761962891</v>
+        <v>0.3367100059986115</v>
       </c>
       <c r="JB64" t="n">
         <v>0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.3191965818405151</v>
+        <v>0.3191965520381927</v>
       </c>
       <c r="JB68" t="n">
         <v>0.3</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.2856564819812775</v>
+        <v>0.2856564521789551</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.7199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.3102104365825653</v>
+        <v>0.3102105557918549</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.2305819988250732</v>
+        <v>0.2305820435285568</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.3933239281177521</v>
+        <v>0.3933239877223969</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.3779951632022858</v>
+        <v>0.3779951930046082</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.523462176322937</v>
+        <v>0.5234622955322266</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3179396688938141</v>
+        <v>0.3179396986961365</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.2721230983734131</v>
+        <v>0.2721231579780579</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.4024220705032349</v>
+        <v>0.4024221003055573</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.7199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.3681215345859528</v>
+        <v>0.3681215643882751</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.7199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.450409471988678</v>
+        <v>0.4504095315933228</v>
       </c>
       <c r="JB82" t="n">
         <v>0.1600000000000001</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.8230204582214355</v>
+        <v>0.8230203986167908</v>
       </c>
       <c r="JB85" t="n">
         <v>0.7199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.8548390865325928</v>
+        <v>0.854839026927948</v>
       </c>
       <c r="JB86" t="n">
         <v>0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.9313003420829773</v>
+        <v>0.9313002824783325</v>
       </c>
       <c r="JB88" t="n">
         <v>0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.1127559244632721</v>
+        <v>0.1127558797597885</v>
       </c>
       <c r="JB89" t="n">
         <v>0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.7527236938476562</v>
+        <v>0.7527236342430115</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.8599999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.386773556470871</v>
+        <v>0.3867734670639038</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.3675996661186218</v>
+        <v>0.3675996363162994</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.5294774174690247</v>
+        <v>0.5294773578643799</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.4059231877326965</v>
+        <v>0.4059231579303741</v>
       </c>
       <c r="JB97" t="n">
         <v>0.02000000000000007</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.1857801526784897</v>
+        <v>0.1857801228761673</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.277698278427124</v>
+        <v>0.2776982188224792</v>
       </c>
       <c r="JB102" t="n">
         <v>0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.3355928063392639</v>
+        <v>0.3355927467346191</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.2320923805236816</v>
+        <v>0.2320923656225204</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.8599999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.1120200529694557</v>
+        <v>0.1120200976729393</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.3010963499546051</v>
+        <v>0.3010964095592499</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.5510005950927734</v>
+        <v>0.5510005354881287</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3084949254989624</v>
+        <v>0.3084949553012848</v>
       </c>
       <c r="JB110" t="n">
         <v>0.16</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.4190325736999512</v>
+        <v>0.4190326929092407</v>
       </c>
       <c r="JB111" t="n">
         <v>0.16</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.2291880697011948</v>
+        <v>0.2291881293058395</v>
       </c>
       <c r="JB113" t="n">
         <v>0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.7123171091079712</v>
+        <v>0.7123170495033264</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.2694237530231476</v>
+        <v>0.2694238126277924</v>
       </c>
       <c r="JB115" t="n">
         <v>0.02000000000000007</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.3101788759231567</v>
+        <v>0.3101789355278015</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.8599999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.3081660866737366</v>
+        <v>0.308166116476059</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.2613233327865601</v>
+        <v>0.2613233923912048</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.8599999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.2335698753595352</v>
+        <v>0.23356993496418</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.8599999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.3990555703639984</v>
+        <v>0.3990556597709656</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.8599999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3496275842189789</v>
+        <v>0.3496276140213013</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.2564267516136169</v>
+        <v>0.2564268410205841</v>
       </c>
       <c r="JB123" t="n">
         <v>0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.4830233752727509</v>
+        <v>0.4830234348773956</v>
       </c>
       <c r="JB124" t="n">
         <v>0.4399999999999999</v>
